--- a/outputs/daily/hr_rankings_2026-10-11.xlsx
+++ b/outputs/daily/hr_rankings_2026-10-11.xlsx
@@ -1078,7 +1078,7 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
@@ -1706,7 +1706,7 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
@@ -2336,7 +2336,7 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
@@ -2690,7 +2690,7 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
@@ -3004,7 +3004,7 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
@@ -3946,7 +3946,7 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
@@ -4260,7 +4260,7 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
@@ -4574,7 +4574,7 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
@@ -5204,7 +5204,7 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
@@ -5558,7 +5558,7 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
@@ -5872,7 +5872,7 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
@@ -6186,7 +6186,7 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
@@ -6500,7 +6500,7 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
@@ -7220,7 +7220,7 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
@@ -7534,7 +7534,7 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
@@ -7848,7 +7848,7 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
@@ -8162,7 +8162,7 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
@@ -8478,7 +8478,7 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
@@ -8832,7 +8832,7 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
@@ -9146,7 +9146,7 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
@@ -9460,7 +9460,7 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
@@ -9774,7 +9774,7 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
@@ -10088,7 +10088,7 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
@@ -10402,7 +10402,7 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
@@ -10716,7 +10716,7 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
@@ -11030,7 +11030,7 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
@@ -11346,7 +11346,7 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
@@ -11700,7 +11700,7 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
@@ -12014,7 +12014,7 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
@@ -12328,7 +12328,7 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
@@ -12642,7 +12642,7 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
